--- a/samples/수주취합/고객사C_발주서.xlsx
+++ b/samples/수주취합/고객사C_발주서.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="62">
   <si>
     <t>No</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>EA</t>
+  </si>
+  <si>
+    <t>KRW</t>
   </si>
   <si>
     <t>4504430002</t>
@@ -838,16 +841,16 @@
         <v>3</v>
       </c>
       <c r="AE2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>3</v>
+        <v>58</v>
+      </c>
+      <c r="AF2">
+        <v>5600</v>
+      </c>
+      <c r="AG2">
+        <v>39200</v>
+      </c>
+      <c r="AH2">
+        <v>1</v>
       </c>
       <c r="AI2" t="s">
         <v>3</v>
@@ -927,7 +930,7 @@
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I3">
         <v>20</v>
@@ -963,10 +966,10 @@
         <v>3</v>
       </c>
       <c r="T3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V3" t="s">
         <v>3</v>
@@ -996,16 +999,16 @@
         <v>3</v>
       </c>
       <c r="AE3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>3</v>
+        <v>58</v>
+      </c>
+      <c r="AF3">
+        <v>150000</v>
+      </c>
+      <c r="AG3">
+        <v>7500</v>
+      </c>
+      <c r="AH3">
+        <v>100</v>
       </c>
       <c r="AI3" t="s">
         <v>3</v>
